--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.96447067299083</v>
+        <v>6.006726484361011</v>
       </c>
       <c r="D2" t="n">
-        <v>37.13956318255148</v>
+        <v>6.035179017164615</v>
       </c>
       <c r="E2" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F2" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.73934308856388</v>
+        <v>5.15764325189163</v>
       </c>
       <c r="D3" t="n">
-        <v>32.90164609225329</v>
+        <v>5.346517489991161</v>
       </c>
       <c r="E3" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F3" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.98462486424114</v>
+        <v>4.710001540439185</v>
       </c>
       <c r="D4" t="n">
-        <v>28.46635656298765</v>
+        <v>4.625782941485494</v>
       </c>
       <c r="E4" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F4" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.58555881994148</v>
+        <v>7.08265330824049</v>
       </c>
       <c r="D5" t="n">
-        <v>42.46518898276508</v>
+        <v>6.900593209699326</v>
       </c>
       <c r="E5" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F5" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.19772774039717</v>
+        <v>3.119630757814539</v>
       </c>
       <c r="D6" t="n">
-        <v>20.63281315688556</v>
+        <v>3.352832137993904</v>
       </c>
       <c r="E6" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F6" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.37879743919226</v>
+        <v>7.211554583868743</v>
       </c>
       <c r="D7" t="n">
-        <v>45.86748137694759</v>
+        <v>7.453465723753983</v>
       </c>
       <c r="E7" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F7" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.04209184045529</v>
+        <v>1.794339924073984</v>
       </c>
       <c r="D8" t="n">
-        <v>11.62867395383228</v>
+        <v>1.889659517497745</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F8" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.77522536130499</v>
+        <v>8.088474121212061</v>
       </c>
       <c r="D9" t="n">
-        <v>38.48432257296764</v>
+        <v>6.253702418107242</v>
       </c>
       <c r="E9" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F9" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.23427203877267</v>
+        <v>5.075569206300559</v>
       </c>
       <c r="D10" t="n">
-        <v>29.67708053826326</v>
+        <v>4.82252558746778</v>
       </c>
       <c r="E10" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F10" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.74310947027629</v>
+        <v>5.808255288919897</v>
       </c>
       <c r="D11" t="n">
-        <v>30.26815038049702</v>
+        <v>4.918574436830767</v>
       </c>
       <c r="E11" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F11" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.66842531266495</v>
+        <v>7.096119113308054</v>
       </c>
       <c r="D12" t="n">
-        <v>27.89705125575632</v>
+        <v>4.533270829060402</v>
       </c>
       <c r="E12" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F12" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.16314854290101</v>
+        <v>4.576511638221414</v>
       </c>
       <c r="D13" t="n">
-        <v>14.15519363774946</v>
+        <v>2.300218966134287</v>
       </c>
       <c r="E13" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F13" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.2937149833542</v>
+        <v>2.322728684795059</v>
       </c>
       <c r="D14" t="n">
-        <v>8.66298396008821</v>
+        <v>1.407734893514334</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F14" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.97323299483412</v>
+        <v>2.758150361660544</v>
       </c>
       <c r="D15" t="n">
-        <v>20.34104657931704</v>
+        <v>3.30542006913902</v>
       </c>
       <c r="E15" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F15" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>13.57065517940702</v>
+        <v>2.205231466653641</v>
       </c>
       <c r="D16" t="n">
-        <v>10.66574877220108</v>
+        <v>1.733184175482676</v>
       </c>
       <c r="E16" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F16" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.20752114402876</v>
+        <v>5.233722185904674</v>
       </c>
       <c r="D17" t="n">
-        <v>29.4476247164509</v>
+        <v>4.785239016423271</v>
       </c>
       <c r="E17" t="n">
-        <v>11.79716781182037</v>
+        <v>1.91703976942081</v>
       </c>
       <c r="F17" t="n">
-        <v>11.12429833279284</v>
+        <v>1.807698479078836</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
